--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488093_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488093_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5528</v>
+        <v>3.302</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0226</v>
+        <v>2.4738</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5302</v>
+        <v>0.8282</v>
       </c>
       <c r="G2" t="n">
         <v>1.8025</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4994</v>
+        <v>0.2486</v>
       </c>
       <c r="T2" t="n">
-        <v>0.382</v>
+        <v>-0.1669</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1175</v>
+        <v>0.4155</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5331</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4631</v>
+        <v>1.1707</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5057</v>
+        <v>0.3303</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0426</v>
+        <v>0.8404</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.251</v>
+        <v>3.7416</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.0315</v>
+        <v>2.5728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7805</v>
+        <v>1.1688</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.6165</v>
+        <v>3.0799</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.7007</v>
+        <v>3.5582</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0842</v>
+        <v>-0.4782</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6346000000000001</v>
+        <v>0.6617</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3308</v>
+        <v>-0.9853</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6962</v>
+        <v>1.647</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6964</v>
+        <v>-0.7691</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3731</v>
+        <v>-0.0934</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6767</v>
+        <v>-0.6757</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4142</v>
+        <v>-1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7403</v>
+        <v>-0.674</v>
       </c>
       <c r="X4" t="n">
-        <v>0.674</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4429</v>
+        <v>0.2388</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0606</v>
+        <v>0.4571</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5034999999999999</v>
+        <v>-0.2184</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7416</v>
+        <v>0.4035</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5728</v>
+        <v>-1.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1688</v>
+        <v>1.5172</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0799</v>
+        <v>0.6673</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5582</v>
+        <v>-0.5782</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4782</v>
+        <v>1.2455</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6617</v>
+        <v>-0.2638</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9853</v>
+        <v>-0.5355</v>
       </c>
       <c r="O5" t="n">
-        <v>1.647</v>
+        <v>0.2717</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.497</v>
+        <v>-0.2946</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4844</v>
+        <v>-0.2101</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0126</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2743</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.471</v>
+        <v>0.839</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1967</v>
+        <v>-0.7583</v>
       </c>
       <c r="G6" t="n">
         <v>1.273</v>
@@ -922,13 +922,13 @@
         <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2679</v>
+        <v>0.0743</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9984</v>
+        <v>-0.6304</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2662</v>
+        <v>0.7046</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8701</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0246</v>
+        <v>-0.1323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3553</v>
+        <v>-0.2863</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3307</v>
+        <v>0.1539</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4035</v>
+        <v>-2.251</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1137</v>
+        <v>-3.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5172</v>
+        <v>0.7805</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6673</v>
+        <v>-1.6165</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5782</v>
+        <v>-1.7007</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2455</v>
+        <v>0.0842</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2638</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5355</v>
+        <v>-1.3308</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2717</v>
+        <v>0.6962</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5088</v>
+        <v>0.1009</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.312</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1968</v>
+        <v>-0.4801</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>2.4142</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MATEOS PENA</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1056</v>
+        <v>-1.3784</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8058</v>
+        <v>-1.7474</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2998</v>
+        <v>0.369</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8332</v>
+        <v>-3.2937</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6107</v>
+        <v>-2.253</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2224</v>
+        <v>-1.0407</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2977</v>
+        <v>-2.5818</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0605</v>
+        <v>-0.5846</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3583</v>
+        <v>-1.9972</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5355</v>
+        <v>-0.7119</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6713</v>
+        <v>-1.6684</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1358</v>
+        <v>0.9565</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5294</v>
+        <v>-0.2918</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4919</v>
+        <v>0.0148</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0374</v>
+        <v>-0.3066</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>A. MATEOS PENA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.497</v>
+        <v>-1.4569</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8098</v>
+        <v>-1.2133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3129</v>
+        <v>-0.2436</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2937</v>
+        <v>-1.8332</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.253</v>
+        <v>-0.6107</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0407</v>
+        <v>-1.2224</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5818</v>
+        <v>-1.2977</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5846</v>
+        <v>0.0605</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9972</v>
+        <v>-1.3583</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7119</v>
+        <v>-0.5355</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6684</v>
+        <v>-0.6713</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9565</v>
+        <v>0.1358</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4104</v>
+        <v>0.1781</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0476</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3628</v>
+        <v>0.0936</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.376</v>
+        <v>-1.5704</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7599</v>
+        <v>-1.7578</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3839</v>
+        <v>0.1874</v>
       </c>
       <c r="G10" t="n">
         <v>0.8841</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.148</v>
+        <v>-0.3424</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0901</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0579</v>
+        <v>-0.2545</v>
       </c>
       <c r="V10" t="n">
         <v>0.2666</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4811</v>
+        <v>-1.6785</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7491</v>
+        <v>-2.115</v>
       </c>
       <c r="F11" t="n">
-        <v>0.268</v>
+        <v>0.4365</v>
       </c>
       <c r="G11" t="n">
         <v>1.5438</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3707</v>
+        <v>-0.5681</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5395</v>
+        <v>0.0946</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8312</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8701</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6849</v>
+        <v>-4.0266</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9335</v>
+        <v>-0.8087</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7514</v>
+        <v>-3.2179</v>
       </c>
       <c r="G12" t="n">
         <v>-1.358</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.197</v>
+        <v>-0.5387</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2972</v>
+        <v>-0.1724</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8999</v>
+        <v>-0.3664</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.270899999999999</v>
+        <v>-3.3349</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.648099999999999</v>
+        <v>-1.7123</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6227</v>
+        <v>-1.6228</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0286</v>
+        <v>3.028600000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-3.026799999999999</v>
@@ -1450,7 +1450,7 @@
         <v>-2.8875</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.026599999999999</v>
+        <v>-3.0266</v>
       </c>
       <c r="N13" t="n">
         <v>-11.9693</v>
@@ -1468,13 +1468,13 @@
         <v>9.911199999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.1388</v>
+        <v>-2.2028</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5222</v>
+        <v>-0.5861</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6168</v>
+        <v>-1.6169</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1960000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.07</v>
+        <v>4.7994</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5809</v>
+        <v>3.0903</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4891</v>
+        <v>1.7092</v>
       </c>
       <c r="G14" t="n">
         <v>3.9557</v>
@@ -1546,13 +1546,13 @@
         <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4871</v>
+        <v>0.2423</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6864</v>
+        <v>-0.177</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1992</v>
+        <v>0.4193</v>
       </c>
       <c r="V14" t="n">
         <v>0.7997</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5334</v>
+        <v>2.2775</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5636</v>
+        <v>1.4617</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9699</v>
+        <v>0.8158</v>
       </c>
       <c r="G15" t="n">
         <v>1.1806</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4389</v>
+        <v>1.183</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.449</v>
       </c>
       <c r="U15" t="n">
-        <v>0.888</v>
+        <v>0.7339</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4737</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1255</v>
+        <v>2.1732</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7747</v>
+        <v>1.2654</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3507</v>
+        <v>0.9077</v>
       </c>
       <c r="G16" t="n">
         <v>2.4385</v>
@@ -1702,13 +1702,13 @@
         <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>0.024</v>
+        <v>0.0716</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3599</v>
+        <v>-0.1494</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3359</v>
+        <v>0.2211</v>
       </c>
       <c r="V16" t="n">
         <v>-0.337</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0061</v>
+        <v>0.8081</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8838</v>
+        <v>1.7436</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1223</v>
+        <v>-0.9355</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6604</v>
+        <v>-0.425</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5246</v>
+        <v>3.4528</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1358</v>
+        <v>-3.8778</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3425</v>
+        <v>1.0153</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0158</v>
+        <v>3.8407</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3583</v>
+        <v>-2.8254</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.318</v>
+        <v>-1.4403</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5404</v>
+        <v>-0.3879</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2224</v>
+        <v>-1.0524</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5947</v>
+        <v>1.9822</v>
       </c>
       <c r="S17" t="n">
-        <v>1.268</v>
+        <v>0.5085</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2262</v>
+        <v>0.5123</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0418</v>
+        <v>-0.0038</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1962</v>
+        <v>-0.2666</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1962</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8563</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6525</v>
+        <v>0.3469</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2038</v>
+        <v>0.335</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1219</v>
@@ -1858,13 +1858,13 @@
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2536</v>
+        <v>1.0793</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9253</v>
+        <v>0.6197</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3284</v>
+        <v>0.4596</v>
       </c>
       <c r="V18" t="n">
         <v>0.9405</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3027</v>
+        <v>0.3952</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3027</v>
+        <v>-0.5535</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.9487</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3027</v>
+        <v>-1.6988</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3027</v>
+        <v>0.2795</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.9783</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3027</v>
+        <v>-0.0607</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3027</v>
+        <v>1.1369</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.1975</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.6381</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.3022</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.8028</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1268</v>
+        <v>0.3027</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8591</v>
+        <v>0.3027</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9859</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6988</v>
+        <v>0.3027</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2795</v>
+        <v>0.3027</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9783</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0607</v>
+        <v>0.3027</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1369</v>
+        <v>0.3027</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1975</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6381</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8574000000000001</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8366</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0034</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.108</v>
+        <v>-0.0022</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5398</v>
+        <v>-0.2368</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4318</v>
+        <v>0.2346</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.425</v>
+        <v>-0.6604</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4528</v>
+        <v>-0.5246</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8778</v>
+        <v>-0.1358</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0153</v>
+        <v>-0.3425</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8407</v>
+        <v>1.0158</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.8254</v>
+        <v>-1.3583</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4403</v>
+        <v>-0.318</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3879</v>
+        <v>-1.5404</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0524</v>
+        <v>1.2224</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1915</v>
+        <v>0.2598</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3085</v>
+        <v>0.1057</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5001</v>
+        <v>0.1541</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2666</v>
+        <v>-0.1962</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9616</v>
+        <v>-0.6253</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.248</v>
+        <v>-1.7386</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2864</v>
+        <v>1.1133</v>
       </c>
       <c r="G22" t="n">
         <v>0.246</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1987</v>
+        <v>0.1376</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4266</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7373</v>
+        <v>0.5642</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.442</v>
+        <v>-1.3697</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1393</v>
+        <v>-1.7318</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3027</v>
+        <v>0.362</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5995</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4022</v>
+        <v>0.67</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0589</v>
+        <v>0.4664</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4612</v>
+        <v>0.2036</v>
       </c>
       <c r="V23" t="n">
         <v>2.9474</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4544</v>
+        <v>-3.1324</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4289</v>
+        <v>-2.3271</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0254</v>
+        <v>-0.8054</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6463</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4027</v>
+        <v>-0.0808</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2155</v>
+        <v>0.0046</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.270800000000001</v>
+        <v>6.3085</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6227</v>
+        <v>1.6228</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6482</v>
+        <v>4.6854</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.028399999999999</v>
+        <v>-3.0284</v>
       </c>
       <c r="H25" t="n">
-        <v>3.0268</v>
+        <v>3.026799999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.055199999999998</v>
+        <v>-6.0552</v>
       </c>
       <c r="J25" t="n">
         <v>3.026600000000001</v>
@@ -2389,7 +2389,7 @@
         <v>-6.055099999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.942699999999999</v>
+        <v>-8.9427</v>
       </c>
       <c r="O25" t="n">
         <v>2.8875</v>
@@ -2404,13 +2404,13 @@
         <v>13.8756</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1389</v>
+        <v>5.176299999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6167</v>
+        <v>1.617</v>
       </c>
       <c r="U25" t="n">
-        <v>1.522</v>
+        <v>3.5594</v>
       </c>
       <c r="V25" t="n">
         <v>0.1960999999999999</v>
